--- a/gs/departures.xlsx
+++ b/gs/departures.xlsx
@@ -150,7 +150,7 @@
     <t>Frontier Airlines</t>
   </si>
   <si>
-    <t>Uber</t>
+    <t>Please arrange an Uber or taxi for your transfer to the airport.</t>
   </si>
   <si>
     <t>Sahid Godoy</t>

--- a/gs/departures.xlsx
+++ b/gs/departures.xlsx
@@ -126,7 +126,7 @@
     <t>DEPARTURE FROM HOTEL</t>
   </si>
   <si>
-    <t>9/11/2026</t>
+    <t>10/8/2026</t>
   </si>
   <si>
     <t>8:10 AM - 8:20 AM</t>

--- a/gs/departures.xlsx
+++ b/gs/departures.xlsx
@@ -141,7 +141,7 @@
     <t>3:25 PM - 7:50  PM</t>
   </si>
   <si>
-    <t>GUSTAVO MENENDEZ</t>
+    <t>Gustavo Menendez</t>
   </si>
   <si>
     <t>Oct 8</t>
@@ -222,7 +222,7 @@
     <t xml:space="preserve">German Rodriguez </t>
   </si>
   <si>
-    <t>EDUARDO ARTAVIA</t>
+    <t>Eduardo Artavia</t>
   </si>
   <si>
     <t>Abdiel Hernandez</t>

--- a/gs/departures.xlsx
+++ b/gs/departures.xlsx
@@ -162,7 +162,7 @@
     <t>PURU</t>
   </si>
   <si>
-    <t>carlos martinez</t>
+    <t>Carlos Martinez</t>
   </si>
   <si>
     <t>Jasson Hernandez</t>
